--- a/docs/files/2026-10-15/상담행정공고_2026-10-15.xlsx
+++ b/docs/files/2026-10-15/상담행정공고_2026-10-15.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$30</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직 · 대체인력</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직 · 대체인력</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -711,35 +711,31 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071300</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1060700</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>사회복지법인 생명의전화</t>
+          <t>의정부시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>[채용공고] 의정부시남자단기청소년쉼터 직원(팀원) 채용 연장공고</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>서울특별시</t>
+          <t>경기도</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
@@ -750,17 +746,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -772,35 +768,35 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071991</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 교육</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>양천해누리복지관</t>
+          <t>학교밖청소년 대안교육기관 내일더하기</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
+          <t>학교밖청소년 대안교육기관 내일더하기 상근교사 채용공고</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 양천구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -811,17 +807,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-10</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr"/>
@@ -833,25 +829,29 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072962</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>우천복지재단</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
+          <t>중랑구청소년커뮤니티공간딩가동4번지 청소년지도사 채용공고</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울특별시 중랑구</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -872,17 +872,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -894,35 +894,35 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072961</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터</t>
+          <t>사회복지법인 생명의전화</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
+          <t>[채용공고]사회복지법인 생명의전화 직원채용(청소년사업팀)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -933,17 +933,17 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-2</t>
+          <t>오늘</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -955,108 +955,96 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담 · 행정</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>주택도시보증공사</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>서울,부산,인천</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>서울특별시 양천구</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-4</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
-        </is>
-      </c>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>청소년</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터</t>
+          <t>우천복지재단</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>경기북부청소년성문화센터 직원 채용공고</t>
+          <t>탈북청소년 런페어 진로사례관리사업 담당자</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 파주시</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
@@ -1067,17 +1055,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>오늘</t>
+          <t>D-1</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1089,7 +1077,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070432</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1090,12 @@
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>시흥시남자단기청소년쉼터</t>
+          <t>강동여자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
+          <t>강동여자단기청소년쉼터 직원채용(보호상담원)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1117,7 +1105,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
@@ -1128,17 +1116,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1150,96 +1138,104 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069566</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년</t>
+          <t>상담 · 행정</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>안양시남자단기청소년쉼터</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
+          <t>2026년 주택도시보증공사 시니어 민원·상담 도우미 채용공고</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>정규직</t>
+          <t>계약직</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
+          <t>서울,부산,인천</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>D-4</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>□ 공통자격 ㆍ 만 60세 이상인 자(입사지원서 접수 마감일 기준) - 한국노인인력개발원의 현장실습 훈련(시니어 인턴십) 지원사업 협약에 따라 참여 자격요건인 만 60세 이상으로 지원자격 설정 ㆍ 국가공무원법 제33조 및 공사 인사규정 제17조(결격사유)에 의한 채용 결격사유에 해당하지 않는 자 ㆍ 임용예정일 이후 즉시 근무 가능한 자(입사 유예 불가)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>□ 장애인, 저소득층, 북한이탈주민, 다문화가족, 의사상자 ㅇ 우대방법: 서류전형 및 면접전형 시 가점 부여(장애인 5% 또는 10%, 의사상자 3% 또는 5%, 그외 3%) □ 취업지원대상자 ㅇ 우대방법: 서류전형 및 면접전형 시 관계법령에 따른 비율(5% 또는 10%)대로 가점 부여 □ 경찰, 청원경찰 등의 근무경력이 있는 자 등 우대(공고문 참조) □ 유의사항 ㅇ 전형별 가점을 제외한 최종점수가 40점(100점 만점) 미만인 경우 우대가점 미적용 ㅇ 우대사항 중복 시 가장 유리한 사항만 적용 ㅇ 취업지원 대상자에 따른 우대사항</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>복지넷</t>
+          <t>잡알리오(공공기관)</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
+          <t>https://www.khug.or.kr/hug/web/ci/re/cire000051.jsp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>청소년 · 복지 · 교육</t>
+          <t>청소년 · 복지</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>율목종합사회복지관</t>
+          <t>아담스지역아동센터</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>계약직</t>
-        </is>
-      </c>
+          <t>(사)들꽃청소년세상 아담스 지역아동센터 생활복지사를 모십니다</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>경기도 안양시 만안구</t>
+          <t>서울특별시</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
@@ -1250,17 +1246,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-11-23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr"/>
@@ -1272,42 +1268,38 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073282</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>복지 · 행정</t>
+          <t>청소년</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>학교법인한국폴리텍</t>
+          <t>경기북부청소년성문화센터</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+          <t>경기북부청소년성문화센터 직원 채용공고</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>청년인턴(체험형)</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>경기</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>학력무관</t>
-        </is>
-      </c>
+          <t>경기도 파주시</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -1315,60 +1307,52 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
-        </is>
-      </c>
+          <t>오늘</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>잡알리오(공공기관)</t>
+          <t>복지넷</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1070721</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>상담 · 청소년</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관</t>
+          <t>시흥시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+          <t>*긴급/상시* 2026년 시흥시남자단기청소년쉼터 보호상담원 채용 공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1384,17 +1368,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1406,7 +1390,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1069317</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1403,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>솔이랑</t>
+          <t>안양시남자단기청소년쉼터</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+          <t>2026년 안양시남자단기청소년쉼터 채용 공고(야간보호상담원)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 중구</t>
+          <t>경기도 안양시</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr"/>
@@ -1445,17 +1429,17 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1467,25 +1451,25 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071439</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>상담 · 복지</t>
+          <t>청소년 · 복지 · 교육</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>아담중증장애인거주시설</t>
+          <t>율목종합사회복지관</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+          <t>2026년 아동청소년특기교육 유아체육 강사 채용 공고</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1495,7 +1479,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>대전광역시 유성구</t>
+          <t>경기도 안양시 만안구</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1506,17 +1490,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr"/>
@@ -1528,12 +1512,809 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1071157</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>복지 · 행정</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>학교법인한국폴리텍</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>한국폴리텍대학 화성캠퍼스 청년인턴(장애인 제한경쟁) 공개채용(2차)공고</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>체험형 인턴</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>경기</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>D-5</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>○ (필수) 장애인고용촉진 및 직업재활법 제2조에 따른 장애인으로 임용(예정)일부터 즉시 근무 가능한 자 ○ (연령) 공고마감일 현재 만 15세 이상 만 34세 이하인 청년 * ?제대군인지원에 관한 법률?에 따라 같은 법 제2조에 의한 제대군인 및 ?병역법? 제26조제1항제1호의 업무에 복무하고 소집 해제된 공익근무요원이 응시할 경우 상한 연령을 연장함(복무기간 1년 미만 1세, 1년 이상 2년 미만 2세, 2년 이상 3세) ○ (학력·전공) 제한 없음 ○ (기타) ① 학교법인한국폴리텍 인사규정 제19조(결격사유) 미해당자 ② 기존 폴리텍 청년인턴 미경험자</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1. 취업지원 대상자 ○「독립유공자 예우에 관한 법률」 ○「국가유공자 등 예우 및 지원에 관한 법률」 ○「5·18민주유공자 예우에 관한 법률」 ○「특수임무유공자 예우 및 단체설립에 관한 법률」 ○「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 ○「보훈보상대상자 지원에 관한 법률」에 따른 취업지원 대상자 2. 장애인 ○「장애인 복지법」에 따른 장애인 등록자 ○「국가유공자 등 예우 및 지원에 관한 법률」에 따른 상이등급 기준에 해당하는 자 ※ 중증장애인은 지역주민센터 및 장애인고용공단의 “중증장애인 확인서” 제출 시에만 인정 3</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>잡알리오(공공기관)</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kopo.ac.kr/hwaseong/board.do?menu=7078&amp;mode=view&amp;post=786987</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>마음드림심리상담센터 광명점</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>발달장애성인주간활동 서비스 및청소년 방과후 제공인력 구함.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>경기도 광명시</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>D-7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073392</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 용인CYA부설마음드림심리상담센터</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>성인발달장애 주간활동 서비스 및 청소년 방과후 서비스 제공인력</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>경기도 용인시</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>D-8</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073393</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>시흥장애인종합복지관 맞춤서비스지원팀 심리운동사 또는 작업치료사 (바우처사업/계약직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>경기도 시흥시</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072587</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>청소년</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>안양시일시청소년쉼터(고정형, 민들레뜨락)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2026년 제4회 안양시일시청소년쉼터 직원 공개경쟁채용 2차 재공고</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안양시</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073477</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>경기해바라기센터(아동)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>경기해바라기센터(아동) 파트타임 임상심리전문가 채용 공고</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>시간제</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>경기도 성남시 분당구</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-12</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072988</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>안산시장애인복지관</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>[채용공고]안산시장애인복지관 심리치료사 공개채용 공고(정규직)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 단원구</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073101</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>안산시장애인복지관</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>[채용공고] 안산시장애인복지관 심리치료사(정규직)</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073092</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>청소년 · 복지</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>빅사랑</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>남자 아동청소년 공동생활가정 생활복지사 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>경기도 안산시 상록구</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>D-16</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072941</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>솔이랑</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>든솔 사회적협동조합 대전지부 학대피해아동쉼터 직원(심리치료사) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>D-1</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068844</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>아담중증장애인거주시설</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>아담 중증장애인거주시설 상담평가요원 모집공고</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 유성구</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072588</t>
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소 '느티나무'</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>사단법인 여성인권티움 부설 &lt;여성인권지원상담소 ‘ 느티나무’&gt;와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시 중구</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1072889</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 복지</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>여성인권지원상담소'느티나무'</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>여성 인권지원상담소 '느티나무'와 함께 할 사회복지사를 모집합니다.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>대전광역시</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>D-13</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1073488</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
